--- a/data/trans_bre/P1421-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1421-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>180,81%</t>
+          <t>202,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,5</t>
+          <t>1,16; 4,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,95</t>
+          <t>2,72; 5,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,28</t>
+          <t>3,22; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,81</t>
+          <t>5,31; 9,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 220,75</t>
+          <t>28,55; 218,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>105,05; 588,11</t>
+          <t>107,36; 553,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>101,63; 517,0</t>
+          <t>104,5; 523,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,0; 325,19</t>
+          <t>96,56; 350,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>123,34%</t>
+          <t>138,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,29</t>
+          <t>2,6; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,97</t>
+          <t>2,58; 4,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,84</t>
+          <t>2,71; 4,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,61</t>
+          <t>5,09; 8,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>103,72; 368,27</t>
+          <t>108,93; 384,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>161,22; 565,31</t>
+          <t>154,69; 550,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>177,52; 609,39</t>
+          <t>171,27; 626,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,0; 213,0</t>
+          <t>90,81; 206,62</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>154,84%</t>
+          <t>151,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,59</t>
+          <t>0,04; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,58</t>
+          <t>3,19; 7,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,58</t>
+          <t>1,42; 6,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,83</t>
+          <t>3,85; 8,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 241,5</t>
+          <t>-3,19; 246,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>186,24; —</t>
+          <t>221,35; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,73; 513,0</t>
+          <t>36,36; 562,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57,93; 299,59</t>
+          <t>63,66; 297,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>140,66%</t>
+          <t>150,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,37</t>
+          <t>2,45; 4,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,01</t>
+          <t>3,3; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,99</t>
+          <t>3,25; 5,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,64</t>
+          <t>5,6; 7,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,9; 221,76</t>
+          <t>86,83; 214,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>211,64; 516,22</t>
+          <t>220,54; 520,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>177,23; 426,39</t>
+          <t>187,15; 454,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,27; 217,28</t>
+          <t>107,7; 198,97</t>
         </is>
       </c>
     </row>
